--- a/Results/single_algorithm/wMKL/Supplement/Chisq_tests.xlsx
+++ b/Results/single_algorithm/wMKL/Supplement/Chisq_tests.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t xml:space="preserve">Comparison</t>
   </si>
@@ -29,10 +29,10 @@
     <t xml:space="preserve">Vital status vs wMKL cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.850436473010073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35402532243346</t>
+    <t xml:space="preserve">0.742632141749944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31695304857063</t>
   </si>
   <si>
     <t xml:space="preserve">0</t>
@@ -41,121 +41,112 @@
     <t xml:space="preserve">Ethnicity vs wMKL cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202324062734301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76437353761743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07</t>
+    <t xml:space="preserve">0.788294573467517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.925699227866</t>
   </si>
   <si>
     <t xml:space="preserve">Race vs wMKL cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.000836731422405326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3717687614429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12</t>
+    <t xml:space="preserve">0.0051839577988868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2748934489998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105</t>
   </si>
   <si>
     <t xml:space="preserve">Lymph node status vs wMKL cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374257595045834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54667007317755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.033</t>
+    <t xml:space="preserve">0.603153378830985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46711462070005</t>
   </si>
   <si>
     <t xml:space="preserve">Histology vs wMKL cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84241148419713e-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.718037337507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.177</t>
+    <t xml:space="preserve">1.19088762301406e-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.492131381143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15</t>
   </si>
   <si>
     <t xml:space="preserve">Menopausal status vs wMKL cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.116191567946556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9094871492581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.068</t>
+    <t xml:space="preserve">0.716221224641793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9154068124083</t>
   </si>
   <si>
     <t xml:space="preserve">PR status vs wMKL cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23702864302046e-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.406569209506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384</t>
+    <t xml:space="preserve">3.44181330297197e-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.427050448155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31</t>
   </si>
   <si>
     <t xml:space="preserve">ER status vs wMKL cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46874016536406e-46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.427360256312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619</t>
+    <t xml:space="preserve">7.34605539591206e-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.040957028954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516</t>
   </si>
   <si>
     <t xml:space="preserve">HER2 status vs wMKL cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00597427731146674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7768558226796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114</t>
+    <t xml:space="preserve">0.00561530328941004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9948598436671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115</t>
   </si>
   <si>
     <t xml:space="preserve">Metastasis vs wMKL cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0146571779589828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4603453507406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.201</t>
+    <t xml:space="preserve">0.368630386385796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60582637973942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.047</t>
   </si>
   <si>
     <t xml:space="preserve">Stage vs wMKL cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0512457284708242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5668924449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.079</t>
+    <t xml:space="preserve">0.014256364135372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6247220628014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.095</t>
   </si>
 </sst>
 </file>
@@ -523,133 +514,133 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
         <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
         <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
         <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
         <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
         <v>44</v>
-      </c>
-      <c r="B12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
